--- a/output/pdf_financials_xlsx/FOOD.xlsx
+++ b/output/pdf_financials_xlsx/FOOD.xlsx
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.452061</v>
+        <v>-0.452061</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.452061</v>
+        <v>-0.452061</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.452061</v>
+        <v>-0.452061</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.452061</v>
+        <v>-0.452061</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.452061</v>
+        <v>-0.452061</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         </is>
       </c>
       <c r="E439" s="5" t="n">
-        <v>0.452061</v>
+        <v>-0.452061</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FOOD.xlsx
+++ b/output/pdf_financials_xlsx/FOOD.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000311</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.772</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -894,10 +894,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-1.349</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.915</v>
       </c>
     </row>
     <row r="13">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.452061</v>
+        <v>-0.45175</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         <v>-20.937</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.145</v>
+        <v>-5.373</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-31.292</v>
+        <v>-30.422</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-123.256</v>
@@ -1570,10 +1570,10 @@
         <v>-16.524</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.433</v>
+        <v>-2.084</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="28">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.452061</v>
+        <v>-0.45175</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         <v>-18.32</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.948</v>
+        <v>-0.176</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-22.472</v>
+        <v>-21.602</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-105.961</v>
@@ -1654,10 +1654,10 @@
         <v>-5.687</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.948</v>
+        <v>5.297</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.128</v>
+        <v>-1.213</v>
       </c>
     </row>
     <row r="30">
@@ -1686,10 +1686,10 @@
         <v>-11.35539536238711</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.3321979731718599</v>
+        <v>-0.0616738853146069</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-5.92562903115227</v>
+        <v>-5.696219220850452</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-39.45142338022086</v>
@@ -1698,10 +1698,10 @@
         <v>-3.373912837124313</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2.583127232756252</v>
+        <v>3.4657611327026</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1.760438124074488</v>
+        <v>-1.00348282166464</v>
       </c>
     </row>
     <row r="31">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.382893</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.51613</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.382893</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.51993</v>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -35273,7 +35273,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -36768,7 +36768,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E437" s="5" t="n">

--- a/output/pdf_financials_xlsx/FOOD.xlsx
+++ b/output/pdf_financials_xlsx/FOOD.xlsx
@@ -924,22 +924,22 @@
         <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.38</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.17</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-5.233</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-5.668</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-5.514</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-5.375</v>
       </c>
     </row>
     <row r="14">
@@ -1558,22 +1558,22 @@
         <v>-20.937</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.373</v>
+        <v>-2.993</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-30.422</v>
+        <v>-28.252</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-123.256</v>
+        <v>-118.023</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-16.524</v>
+        <v>-10.856</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.084</v>
+        <v>3.43</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.17</v>
+        <v>-1.795</v>
       </c>
     </row>
     <row r="28">
@@ -1642,22 +1642,22 @@
         <v>-18.32</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.176</v>
+        <v>2.204</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-21.602</v>
+        <v>-19.432</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-105.961</v>
+        <v>-100.728</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.687</v>
+        <v>-0.019</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.297</v>
+        <v>10.811</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.213</v>
+        <v>4.162</v>
       </c>
     </row>
     <row r="30">
@@ -1686,22 +1686,22 @@
         <v>-11.35539536238711</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.0616738853146069</v>
+        <v>0.7723252456442818</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-5.696219220850452</v>
+        <v>-5.124013142281546</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-39.45142338022086</v>
+        <v>-37.50307164185773</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-3.373912837124313</v>
+        <v>-0.01127208438638332</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>3.4657611327026</v>
+        <v>7.073502662950314</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1.00348282166464</v>
+        <v>3.443112534021625</v>
       </c>
     </row>
     <row r="31">
@@ -21960,7 +21960,11 @@
           <t>Additions to intangible assets 15</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -23608,7 +23612,11 @@
           <t>Additions to intangible assets 14</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -32689,7 +32697,11 @@
           <t>Net finance costs 8</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -33848,7 +33860,11 @@
           <t>Net finance costs 7</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -34788,7 +34804,11 @@
           <t>Net finance costs 6</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FOOD.xlsx
+++ b/output/pdf_financials_xlsx/FOOD.xlsx
@@ -531,10 +531,8 @@
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>2.80166</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>19.79624</v>
@@ -573,10 +571,8 @@
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>2.53442</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>16.206503</v>
@@ -615,10 +611,8 @@
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0.26724</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>3.589737</v>
@@ -657,10 +651,8 @@
       <c r="B7" s="3" t="n">
         <v>0.068782</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>1.132721</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>7.360829</v>
@@ -699,10 +691,8 @@
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -741,10 +731,8 @@
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -783,10 +771,8 @@
       <c r="B10" s="3" t="n">
         <v>0.452061</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>1.150928</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>9.220271</v>
@@ -825,10 +811,8 @@
       <c r="B11" s="3" t="n">
         <v>-0.452061</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-0.883688</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-5.630534</v>
@@ -867,10 +851,8 @@
       <c r="B12" s="3" t="n">
         <v>-0.000311</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>-0.022431</v>
@@ -909,10 +891,8 @@
       <c r="B13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -951,10 +931,8 @@
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -993,10 +971,8 @@
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1035,10 +1011,8 @@
       <c r="B16" s="3" t="n">
         <v>-0.452061</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-1.239171</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-9.866047</v>
@@ -1077,10 +1051,8 @@
       <c r="B17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1243,10 +1215,8 @@
       <c r="B20" s="3" t="n">
         <v>-0.452061</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-1.239171</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-9.866047</v>
@@ -1285,10 +1255,8 @@
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1327,10 +1295,8 @@
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1369,10 +1335,8 @@
       <c r="B23" s="3" t="n">
         <v>-0.452061</v>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-1.239171</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-9.866047</v>
@@ -1413,10 +1377,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.05</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.32</v>
@@ -1457,10 +1419,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.05</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.32</v>
@@ -1501,10 +1461,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>24.78342</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.831397</v>
@@ -1543,10 +1501,8 @@
       <c r="B27" s="3" t="n">
         <v>-0.45175</v>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-1.239171</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-9.843616000000001</v>
@@ -1585,10 +1541,8 @@
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0.009741</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.054032</v>
@@ -1627,10 +1581,8 @@
       <c r="B29" s="3" t="n">
         <v>-0.45175</v>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-1.22943</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-9.789584</v>
@@ -1671,10 +1623,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v>-43.88219841094209</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-49.45173426872982</v>
@@ -1713,10 +1663,8 @@
       <c r="B31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -1757,10 +1705,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v>-44.22988513952443</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>-49.8379843849135</v>
@@ -2059,22 +2005,22 @@
         <v>2.012</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.638</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>1.949</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="41">
@@ -3152,7 +3098,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.030984</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -3167,13 +3113,13 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>14.81</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>22.129</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>10.294</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -3284,25 +3230,25 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>5.443</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>8.468</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>2.862</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>3.149</v>
       </c>
     </row>
     <row r="71">
@@ -3324,25 +3270,25 @@
         <v>0.528</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.031</v>
+        <v>1.304</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.656</v>
+        <v>3.646</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.651</v>
+        <v>6.094</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.651</v>
+        <v>9.119</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>2.862</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>3.149</v>
       </c>
     </row>
     <row r="72">
@@ -3484,25 +3430,25 @@
         <v>0.5</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.813</v>
+        <v>1.54</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>12.053</v>
+        <v>9.063000000000001</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>5.443</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>19.56</v>
+        <v>11.092</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>6.898</v>
+        <v>4.036</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>10.128</v>
+        <v>7.167</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>3.149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3606,25 +3552,25 @@
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>11.451</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>20.358</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>67.66800000000001</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>60.741</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>10.502</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>10.37</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>7.784</v>
       </c>
     </row>
     <row r="79">
@@ -3646,25 +3592,25 @@
         <v>1.564</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>12.46</v>
+        <v>23.911</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>11.959</v>
+        <v>32.317</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>20.7</v>
+        <v>88.36799999999999</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>20.7</v>
+        <v>81.441</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0</v>
+        <v>10.502</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0</v>
+        <v>10.37</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>7.784</v>
       </c>
     </row>
     <row r="80">
@@ -3688,31 +3634,25 @@
         <v>0.1271268838113758</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.7178323084880179</v>
+        <v>1.449054652031492</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.2249906365371239</v>
+        <v>0.6414061245964794</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.2181455938697318</v>
+        <v>0.9651289910600256</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-1.910091250670961</v>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.101628198246555</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.5700878764610529</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>-0.5111971776976763</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-0.4009608684490409</v>
       </c>
     </row>
     <row r="81">
@@ -3894,22 +3834,22 @@
         <v>1.396</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>50.922</v>
+        <v>39.471</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>34.552</v>
+        <v>14.194</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>73.291</v>
+        <v>5.623</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>67.51000000000001</v>
+        <v>6.769</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>52.254</v>
+        <v>41.752</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>49.746</v>
+        <v>39.376</v>
       </c>
       <c r="L85" s="3" t="n">
         <v>1.035</v>
@@ -4417,10 +4357,8 @@
       <c r="B99" s="3" t="n">
         <v>-0.452061</v>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-1.239171</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-9.866047</v>
@@ -4459,10 +4397,8 @@
       <c r="B100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0.009741</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0.054032</v>
@@ -4501,10 +4437,8 @@
       <c r="B101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -4543,10 +4477,8 @@
       <c r="B102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>-0.07427599999999999</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>-0.303174</v>
@@ -4585,13 +4517,11 @@
       <c r="B103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.13145</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -4627,10 +4557,8 @@
       <c r="B104" s="3" t="n">
         <v>0.031284</v>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.432682</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>2.551633</v>
@@ -4669,10 +4597,8 @@
       <c r="B105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0.011143</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0.818014</v>
@@ -4711,13 +4637,11 @@
       <c r="B106" s="3" t="n">
         <v>-0.287815</v>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.369549</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>3.066473</v>
+        <v>2.935023</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>8.585000000000001</v>
@@ -4726,22 +4650,22 @@
         <v>18.132</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-11.108</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-6.138</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-1.184</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-1.895</v>
       </c>
     </row>
     <row r="107">
@@ -4753,10 +4677,8 @@
       <c r="B107" s="3" t="n">
         <v>0.1125</v>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0.219612</v>
@@ -4768,22 +4690,22 @@
         <v>1.81</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>1.874</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>5.876</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>3.903</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.864</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="108">
@@ -4795,10 +4717,8 @@
       <c r="B108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -4837,10 +4757,8 @@
       <c r="B109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -4879,10 +4797,8 @@
       <c r="B110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0.013806</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0.022534</v>
@@ -4921,10 +4837,8 @@
       <c r="B111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -4963,10 +4877,8 @@
       <c r="B112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -5005,10 +4917,8 @@
       <c r="B113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -5047,10 +4957,8 @@
       <c r="B114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -5089,10 +4997,8 @@
       <c r="B115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -5131,19 +5037,17 @@
       <c r="B116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>-0.04977</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.041366</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.246</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -5173,10 +5077,8 @@
       <c r="B117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -5215,10 +5117,8 @@
       <c r="B118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -5307,10 +5207,8 @@
       <c r="B120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0.006409</v>
@@ -5349,10 +5247,8 @@
       <c r="B121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -5391,10 +5287,8 @@
       <c r="B122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -5433,10 +5327,8 @@
       <c r="B123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -5475,10 +5367,8 @@
       <c r="B124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>-0.024609</v>
@@ -5517,10 +5407,8 @@
       <c r="B125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>-0.024609</v>
@@ -5559,10 +5447,8 @@
       <c r="B126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -5663,10 +5549,8 @@
       <c r="B128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>-1.532507</v>
@@ -5755,10 +5639,8 @@
       <c r="B130" s="3" t="n">
         <v>0.382893</v>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>0.084886</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.51993</v>
@@ -5797,10 +5679,8 @@
       <c r="B131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -5839,10 +5719,8 @@
       <c r="B132" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>0.431244</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>17.028487</v>
@@ -5881,10 +5759,8 @@
       <c r="B133" s="3" t="n">
         <v>0.382893</v>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.51613</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>17.548417</v>
@@ -5923,10 +5799,8 @@
       <c r="B134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6017,7 +5891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6730,7 +6604,11 @@
           <t>Intangible assets and goodwill 15</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -7278,7 +7156,11 @@
           <t>Current portion of lease obligations 19</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -7465,7 +7347,11 @@
           <t>Lease obligations 19</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -9914,7 +9800,11 @@
           <t>Current portion of lease obligations 17</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -10048,7 +9938,11 @@
           <t>Lease obligations 17</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14975,7 +14869,11 @@
           <t>Current portion of lease obligations 20 8,468</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -15192,7 +15090,11 @@
           <t>Lease obligations 20 60,741</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -17794,7 +17696,11 @@
           <t>Current portion of lease obligations 14</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -17938,7 +17844,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -21006,10 +20916,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F211" s="5" t="n">
+        <v>-1.239171</v>
       </c>
       <c r="G211" s="5" t="n">
         <v>-9.866047</v>
@@ -21268,7 +21176,11 @@
           <t>Share-based payments expense 22</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -21402,7 +21314,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -21548,7 +21464,11 @@
           <t>Change in non-cash operating working capital 23</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -23204,7 +23124,11 @@
           <t>Share-based payments expense 19</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -23336,7 +23260,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -23405,7 +23333,11 @@
           <t>Change in non-cash operating working capital 20</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -27097,7 +27029,11 @@
           <t>Share-based payments expense 21</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -27235,7 +27171,11 @@
           <t>Deferred income tax expense (recovery) 7</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -27304,7 +27244,11 @@
           <t>Change in non-cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -28306,10 +28250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F315" s="5" t="n">
+        <v>0.009741</v>
       </c>
       <c r="G315" s="5" t="n">
         <v>0.054032</v>
@@ -28517,10 +28459,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F318" s="5" t="n">
+        <v>0.008466</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -28728,10 +28668,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F321" s="5" t="n">
+        <v>-0.081248</v>
       </c>
       <c r="G321" s="5" t="n">
         <v>-0.692214</v>
@@ -28799,10 +28737,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F322" s="5" t="n">
+        <v>-0.07427599999999999</v>
       </c>
       <c r="G322" s="5" t="n">
         <v>-0.303174</v>
@@ -28937,10 +28873,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F324" s="5" t="n">
+        <v>0.432682</v>
       </c>
       <c r="G324" s="5" t="n">
         <v>2.551633</v>
@@ -29008,10 +28942,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F325" s="5" t="n">
+        <v>0.011143</v>
       </c>
       <c r="G325" s="5" t="n">
         <v>0.818014</v>
@@ -29075,10 +29007,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F326" s="5" t="n">
+        <v>-0.5921110000000001</v>
       </c>
       <c r="G326" s="5" t="n">
         <v>-1.885294</v>
@@ -30051,7 +29981,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -30126,10 +30060,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F341" s="5" t="n">
+        <v>-0.139628</v>
       </c>
       <c r="G341" s="5" t="n">
         <v>-1.853143</v>
@@ -30197,10 +30129,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F342" s="5" t="n">
+        <v>0.431244</v>
       </c>
       <c r="G342" s="5" t="n">
         <v>17.028487</v>
@@ -30268,10 +30198,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F343" s="5" t="n">
+        <v>0.084886</v>
       </c>
       <c r="G343" s="5" t="n">
         <v>0.51993</v>
@@ -31116,10 +31044,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F355" s="5" t="n">
+        <v>0.013806</v>
       </c>
       <c r="G355" s="5" t="n">
         <v>0.022534</v>
@@ -31187,10 +31113,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F356" s="5" t="n">
+        <v>0.201794</v>
       </c>
       <c r="G356" s="5" t="n">
         <v>0.231865</v>
@@ -31611,7 +31535,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -31690,10 +31618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F363" s="5" t="n">
+        <v>0.51613</v>
       </c>
       <c r="G363" s="5" t="n">
         <v>17.548417</v>
@@ -31745,31 +31671,31 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Share-based payment expense</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E364" s="5" t="n">
-        <v>-0.452061</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G364" s="5" t="n">
+        <v>0.219612</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
@@ -31820,31 +31746,25 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E365" s="5" t="n">
-        <v>0.1125</v>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss on remeasurement to fair value of convertible notes</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="n">
+        <v>0.345194</v>
+      </c>
+      <c r="G365" s="5" t="n">
+        <v>4.257944</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
@@ -31895,31 +31815,25 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E366" s="5" t="n">
-        <v>0.031284</v>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other net finance (income) expenses</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F366" s="5" t="n">
+        <v>0.010289</v>
+      </c>
+      <c r="G366" s="5" t="n">
+        <v>-0.022431</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
@@ -31970,27 +31884,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Due to directors and officers</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
-      <c r="E367" s="5" t="n">
-        <v>0.020462</v>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F367" s="5" t="n">
+        <v>-0.009016</v>
+      </c>
+      <c r="G367" s="5" t="n">
+        <v>-0.041271</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
@@ -32041,31 +31957,25 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital total</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E368" s="5" t="n">
-        <v>-0.287815</v>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F368" s="5" t="n">
+        <v>0.000395</v>
+      </c>
+      <c r="G368" s="5" t="n">
+        <v>0.041788</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
@@ -32116,27 +32026,27 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Consideration transferred for Mira VII in excess</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Net proceeds on issuance of common stock</t>
+          <t>Consideration transferred for Mira VII in excess of net assets acquired (note 4)</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
-      <c r="E369" s="5" t="n">
-        <v>0.670708</v>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G369" s="5" t="n">
+        <v>1.262644</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -32187,31 +32097,25 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Consideration transferred for Mira VII in excess</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Net change in cash during the period and cash end of period $</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E370" s="5" t="n">
-        <v>0.382893</v>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deposits included in non-current assets</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F370" s="5" t="n">
+        <v>-0.020116</v>
+      </c>
+      <c r="G370" s="5" t="n">
+        <v>-0.056942</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
@@ -32257,18 +32161,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Change in non-cash operating working capital</t>
+        </is>
+      </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Net sales $</t>
+          <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -32281,10 +32189,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G371" s="5" t="n">
+        <v>-0.13145</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
@@ -32296,40 +32202,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J371" s="5" t="n">
-        <v>285.372</v>
-      </c>
-      <c r="K371" s="5" t="n">
-        <v>379.234</v>
-      </c>
-      <c r="L371" s="5" t="n">
-        <v>268.586</v>
-      </c>
-      <c r="M371" s="5" t="n">
-        <v>168.558</v>
-      </c>
-      <c r="N371" s="5" t="n">
-        <v>152.838</v>
-      </c>
-      <c r="O371" s="5" t="n">
-        <v>120.879</v>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of common shares from</t>
+        </is>
+      </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
+          <t>Proceeds from issuance of common shares from private placement</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -32343,114 +32265,142 @@
         </is>
       </c>
       <c r="G372" s="5" t="n">
-        <v>16.206503</v>
-      </c>
-      <c r="H372" s="5" t="n">
-        <v>55.842</v>
-      </c>
-      <c r="I372" s="5" t="n">
-        <v>121.023</v>
-      </c>
-      <c r="J372" s="5" t="n">
-        <v>198.953</v>
-      </c>
-      <c r="K372" s="5" t="n">
-        <v>263.14</v>
-      </c>
-      <c r="L372" s="5" t="n">
-        <v>200.531</v>
-      </c>
-      <c r="M372" s="5" t="n">
-        <v>103.178</v>
-      </c>
-      <c r="N372" s="5" t="n">
-        <v>89.86</v>
-      </c>
-      <c r="O372" s="5" t="n">
-        <v>70.48</v>
+        <v>21.085766</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of stock options                             6,409             −</t>
+        </is>
+      </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of convertible notes</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F373" s="5" t="n">
+        <v>0.161174</v>
       </c>
       <c r="G373" s="5" t="n">
-        <v>3.589737</v>
-      </c>
-      <c r="H373" s="5" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="I373" s="5" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="J373" s="5" t="n">
-        <v>86.419</v>
-      </c>
-      <c r="K373" s="5" t="n">
-        <v>116.094</v>
-      </c>
-      <c r="L373" s="5" t="n">
-        <v>68.05500000000001</v>
-      </c>
-      <c r="M373" s="5" t="n">
-        <v>65.38</v>
-      </c>
-      <c r="N373" s="5" t="n">
-        <v>62.978</v>
-      </c>
-      <c r="O373" s="5" t="n">
-        <v>50.399</v>
+        <v>1</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of stock options                             6,409             −</t>
+        </is>
+      </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of preferred shares</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F374" s="5" t="n">
+        <v>0.800015</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
@@ -32467,35 +32417,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J374" s="5" t="n">
-        <v>84.98699999999999</v>
-      </c>
-      <c r="K374" s="5" t="n">
-        <v>136.396</v>
-      </c>
-      <c r="L374" s="5" t="n">
-        <v>115.956</v>
-      </c>
-      <c r="M374" s="5" t="n">
-        <v>65.867</v>
-      </c>
-      <c r="N374" s="5" t="n">
-        <v>54.843</v>
-      </c>
-      <c r="O374" s="5" t="n">
-        <v>45.363</v>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of stock options                             6,409             −</t>
+        </is>
+      </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Reorganization and other related net costs (gains) 6</t>
+          <t>Proceeds from exercise of stock options                             6,409             − total</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -32504,15 +32470,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F375" s="5" t="n">
+        <v>1.162983</v>
+      </c>
+      <c r="G375" s="5" t="n">
+        <v>20.766924</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -32544,44 +32506,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N375" s="5" t="n">
-        <v>-1.327</v>
-      </c>
-      <c r="O375" s="5" t="n">
-        <v>1.789</v>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 13,14,15</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Acquisition of fixed assets (note 10)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F376" s="5" t="n">
+        <v>-0.080558</v>
+      </c>
+      <c r="G376" s="5" t="n">
+        <v>-1.811777</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
@@ -32613,40 +32575,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N376" s="5" t="n">
-        <v>7.381</v>
-      </c>
-      <c r="O376" s="5" t="n">
-        <v>5.957</v>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Operating (loss) income</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>Acquisition of intangible assets</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F377" s="5" t="n">
+        <v>-0.04977</v>
+      </c>
+      <c r="G377" s="5" t="n">
+        <v>-0.041366</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
@@ -32678,39 +32648,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N377" s="5" t="n">
-        <v>2.081</v>
-      </c>
-      <c r="O377" s="5" t="n">
-        <v>-2.71</v>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Net finance costs 8</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
+          <t>Short-term investments</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F378" s="5" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -32747,39 +32719,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N378" s="5" t="n">
-        <v>5.514</v>
-      </c>
-      <c r="O378" s="5" t="n">
-        <v>5.375</v>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Investing</t>
+        </is>
+      </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Bank deposits included in other non-current assets</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F379" s="5" t="n">
+        <v>-0.0055</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -32796,46 +32770,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J379" s="5" t="n">
-        <v>-6.145</v>
-      </c>
-      <c r="K379" s="5" t="n">
-        <v>-31.292</v>
-      </c>
-      <c r="L379" s="5" t="n">
-        <v>-123.256</v>
-      </c>
-      <c r="M379" s="5" t="n">
-        <v>-16.524</v>
-      </c>
-      <c r="N379" s="5" t="n">
-        <v>-3.433</v>
-      </c>
-      <c r="O379" s="5" t="n">
-        <v>-8.085000000000001</v>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Income tax expense 9</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="n">
+        <v>-0.452061</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32882,31 +32870,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O380" s="5" t="n">
-        <v>0.01</v>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Net loss, being comprehensive loss $</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="n">
+        <v>0.1125</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32933,43 +32925,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K381" s="5" t="n">
-        <v>-31.792</v>
-      </c>
-      <c r="L381" s="5" t="n">
-        <v>-121.761</v>
-      </c>
-      <c r="M381" s="5" t="n">
-        <v>-16.463</v>
-      </c>
-      <c r="N381" s="5" t="n">
-        <v>-3.433</v>
-      </c>
-      <c r="O381" s="5" t="n">
-        <v>-8.095000000000001</v>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital</t>
+        </is>
+      </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="n">
+        <v>0.031284</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32991,50 +32995,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J382" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="K382" s="5" t="n">
-        <v>-4.5e-07</v>
-      </c>
-      <c r="L382" s="5" t="n">
-        <v>-1.62e-06</v>
-      </c>
-      <c r="M382" s="5" t="n">
-        <v>-2.2e-07</v>
-      </c>
-      <c r="N382" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="O382" s="5" t="n">
-        <v>-9e-08</v>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding 21</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Due to directors and officers</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" s="5" t="n">
+        <v>0.020462</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33076,34 +33086,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N383" s="5" t="n">
-        <v>76.928635</v>
-      </c>
-      <c r="O383" s="5" t="n">
-        <v>86.759641</v>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>8.       NET FINANCE COSTS</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Interest expense on debentures, including accretion interest $</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net changes in non-cash working capital total</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E384" s="5" t="n">
+        <v>-0.287815</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33145,34 +33161,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N384" s="5" t="n">
-        <v>5.725</v>
-      </c>
-      <c r="O384" s="5" t="n">
-        <v>5.705</v>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>8.       NET FINANCE COSTS</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Interest expense on lease obligations</t>
+          <t>Net proceeds on issuance of common stock</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E385" s="5" t="n">
+        <v>0.670708</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33214,38 +33232,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N385" s="5" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="O385" s="5" t="n">
-        <v>0.862</v>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>8.       NET FINANCE COSTS</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net change in cash during the period and cash end of period $</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="n">
+        <v>0.382893</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33287,11 +33307,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N386" s="5" t="n">
-        <v>-1.349</v>
-      </c>
-      <c r="O386" s="5" t="n">
-        <v>-0.915</v>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -33300,17 +33324,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>8.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B387" t="inlineStr"/>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Fair value gain in marketable securities</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>Net sales $</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -33336,33 +33360,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J387" s="5" t="n">
+        <v>285.372</v>
+      </c>
+      <c r="K387" s="5" t="n">
+        <v>379.234</v>
+      </c>
+      <c r="L387" s="5" t="n">
+        <v>268.586</v>
+      </c>
+      <c r="M387" s="5" t="n">
+        <v>168.558</v>
+      </c>
+      <c r="N387" s="5" t="n">
+        <v>152.838</v>
       </c>
       <c r="O387" s="5" t="n">
-        <v>-0.424</v>
+        <v>120.879</v>
       </c>
     </row>
     <row r="388">
@@ -33371,67 +33385,51 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>8.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B388" t="inlineStr"/>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Interest expense on debt</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F388" s="5" t="n">
+        <v>2.53442</v>
+      </c>
+      <c r="G388" s="5" t="n">
+        <v>16.206503</v>
+      </c>
+      <c r="H388" s="5" t="n">
+        <v>55.842</v>
+      </c>
+      <c r="I388" s="5" t="n">
+        <v>121.023</v>
+      </c>
+      <c r="J388" s="5" t="n">
+        <v>198.953</v>
+      </c>
+      <c r="K388" s="5" t="n">
+        <v>263.14</v>
+      </c>
+      <c r="L388" s="5" t="n">
+        <v>200.531</v>
+      </c>
+      <c r="M388" s="5" t="n">
+        <v>103.178</v>
       </c>
       <c r="N388" s="5" t="n">
-        <v>0.259</v>
+        <v>89.86</v>
       </c>
       <c r="O388" s="5" t="n">
-        <v>0.026</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="389">
@@ -33440,67 +33438,51 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>8.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Other finance costs</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F389" s="5" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>3.589737</v>
+      </c>
+      <c r="H389" s="5" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="I389" s="5" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="J389" s="5" t="n">
+        <v>86.419</v>
+      </c>
+      <c r="K389" s="5" t="n">
+        <v>116.094</v>
+      </c>
+      <c r="L389" s="5" t="n">
+        <v>68.05500000000001</v>
+      </c>
+      <c r="M389" s="5" t="n">
+        <v>65.38</v>
       </c>
       <c r="N389" s="5" t="n">
-        <v>0.044</v>
+        <v>62.978</v>
       </c>
       <c r="O389" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>50.399</v>
       </c>
     </row>
     <row r="390">
@@ -33509,19 +33491,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>8.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -33549,31 +33527,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J390" s="5" t="n">
+        <v>84.98699999999999</v>
+      </c>
+      <c r="K390" s="5" t="n">
+        <v>136.396</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>115.956</v>
+      </c>
+      <c r="M390" s="5" t="n">
+        <v>65.867</v>
       </c>
       <c r="N390" s="5" t="n">
-        <v>0.029</v>
+        <v>54.843</v>
       </c>
       <c r="O390" s="5" t="n">
-        <v>0.035</v>
+        <v>45.363</v>
       </c>
     </row>
     <row r="391">
@@ -33582,14 +33552,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>8.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
         <is>
-          <t>8.       NET FINANCE COSTS total</t>
+          <t>Reorganization and other related net costs (gains) 6</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -33639,10 +33605,10 @@
         </is>
       </c>
       <c r="N391" s="5" t="n">
-        <v>5.514</v>
+        <v>-1.327</v>
       </c>
       <c r="O391" s="5" t="n">
-        <v>5.375</v>
+        <v>1.789</v>
       </c>
     </row>
     <row r="392">
@@ -33654,10 +33620,14 @@
       <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Reorganization and other related net gains 6</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
+          <t>Depreciation and amortization 13,14,15</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -33698,16 +33668,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M392" s="5" t="n">
-        <v>-0.468</v>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N392" s="5" t="n">
-        <v>-1.327</v>
-      </c>
-      <c r="O392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.381</v>
+      </c>
+      <c r="O392" s="5" t="n">
+        <v>5.957</v>
       </c>
     </row>
     <row r="393">
@@ -33719,14 +33689,10 @@
       <c r="B393" t="inlineStr"/>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 12,13,14</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Operating (loss) income</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -33767,16 +33733,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M393" s="5" t="n">
-        <v>10.837</v>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N393" s="5" t="n">
-        <v>7.381</v>
-      </c>
-      <c r="O393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.081</v>
+      </c>
+      <c r="O393" s="5" t="n">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="394">
@@ -33788,12 +33754,12 @@
       <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Operating income (loss)</t>
+          <t>Net finance costs 8</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>InterestExpenseNonOperating</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -33836,16 +33802,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M394" s="5" t="n">
-        <v>-10.856</v>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N394" s="5" t="n">
-        <v>2.081</v>
-      </c>
-      <c r="O394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.514</v>
+      </c>
+      <c r="O394" s="5" t="n">
+        <v>5.375</v>
       </c>
     </row>
     <row r="395">
@@ -33857,12 +33823,12 @@
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Net finance costs 7</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestExpenseNonOperating</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -33890,27 +33856,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J395" s="5" t="n">
+        <v>-6.145</v>
       </c>
       <c r="K395" s="5" t="n">
-        <v>2.17</v>
+        <v>-31.292</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>5.233</v>
+        <v>-123.256</v>
       </c>
       <c r="M395" s="5" t="n">
-        <v>5.668</v>
+        <v>-16.524</v>
       </c>
       <c r="N395" s="5" t="n">
-        <v>5.514</v>
-      </c>
-      <c r="O395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.433</v>
+      </c>
+      <c r="O395" s="5" t="n">
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="396">
@@ -33922,10 +33884,14 @@
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 8</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr"/>
+          <t>Income tax expense 9</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -33961,21 +33927,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L396" s="5" t="n">
-        <v>-1.495</v>
-      </c>
-      <c r="M396" s="5" t="n">
-        <v>-0.061</v>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N396" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O396" s="5" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="397">
@@ -33984,19 +33952,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Basic and diluted weighted average number of common</t>
-        </is>
-      </c>
+      <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding 18</t>
+          <t>Net loss, being comprehensive loss $</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -34029,26 +33993,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K397" s="5" t="n">
+        <v>-31.792</v>
+      </c>
+      <c r="L397" s="5" t="n">
+        <v>-121.761</v>
       </c>
       <c r="M397" s="5" t="n">
-        <v>76.103206</v>
+        <v>-16.463</v>
       </c>
       <c r="N397" s="5" t="n">
-        <v>76.928635</v>
-      </c>
-      <c r="O397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.433</v>
+      </c>
+      <c r="O397" s="5" t="n">
+        <v>-8.095000000000001</v>
       </c>
     </row>
     <row r="398">
@@ -34060,10 +34018,14 @@
       <c r="B398" t="inlineStr"/>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Impairment of non-financial assets 6,12,13,14</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -34089,33 +34051,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J398" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="K398" s="5" t="n">
+        <v>-4.5e-07</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>46.085</v>
-      </c>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.62e-06</v>
+      </c>
+      <c r="M398" s="5" t="n">
+        <v>-2.2e-07</v>
+      </c>
+      <c r="N398" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="O398" s="5" t="n">
+        <v>-9e-08</v>
       </c>
     </row>
     <row r="399">
@@ -34124,13 +34076,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Basic and diluted weighted average number of common</t>
+        </is>
+      </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Reorganization and other related (gains) costs 6</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr"/>
+          <t>Basic and diluted weighted average number of common shares outstanding 21</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -34166,21 +34126,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L399" s="5" t="n">
-        <v>6.742</v>
-      </c>
-      <c r="M399" s="5" t="n">
-        <v>-0.468</v>
-      </c>
-      <c r="N399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N399" s="5" t="n">
+        <v>76.928635</v>
+      </c>
+      <c r="O399" s="5" t="n">
+        <v>86.759641</v>
       </c>
     </row>
     <row r="400">
@@ -34189,17 +34149,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 12,13,14,20</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Interest expense on debentures, including accretion interest $</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -34235,21 +34195,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L400" s="5" t="n">
-        <v>17.295</v>
-      </c>
-      <c r="M400" s="5" t="n">
-        <v>10.837</v>
-      </c>
-      <c r="N400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N400" s="5" t="n">
+        <v>5.725</v>
+      </c>
+      <c r="O400" s="5" t="n">
+        <v>5.705</v>
       </c>
     </row>
     <row r="401">
@@ -34258,17 +34218,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Interest expense on lease obligations</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -34294,27 +34254,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J401" s="5" t="n">
-        <v>-3.765</v>
-      </c>
-      <c r="K401" s="5" t="n">
-        <v>-29.122</v>
-      </c>
-      <c r="L401" s="5" t="n">
-        <v>-118.023</v>
-      </c>
-      <c r="M401" s="5" t="n">
-        <v>-10.856</v>
-      </c>
-      <c r="N401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N401" s="5" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="O401" s="5" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="402">
@@ -34323,15 +34287,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding 18</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -34369,21 +34337,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L402" s="5" t="n">
-        <v>74.982435</v>
-      </c>
-      <c r="M402" s="5" t="n">
-        <v>76.103206</v>
-      </c>
-      <c r="N402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N402" s="5" t="n">
+        <v>-1.349</v>
+      </c>
+      <c r="O402" s="5" t="n">
+        <v>-0.915</v>
       </c>
     </row>
     <row r="403">
@@ -34392,17 +34360,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 13,14,15, 23</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Fair value gain in marketable securities</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -34433,11 +34401,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K403" s="5" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="L403" s="5" t="n">
-        <v>17.295</v>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M403" t="inlineStr">
         <is>
@@ -34449,10 +34421,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O403" s="5" t="n">
+        <v>-0.424</v>
       </c>
     </row>
     <row r="404">
@@ -34461,10 +34431,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Impairment of non-financial assets 6, 13,14,15</t>
+          <t>Interest expense on debt</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -34503,23 +34477,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L404" s="5" t="n">
-        <v>46.085</v>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N404" s="5" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="O404" s="5" t="n">
+        <v>0.026</v>
       </c>
     </row>
     <row r="405">
@@ -34528,10 +34500,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Reorganization and other related costs 6</t>
+          <t>Other finance costs</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -34570,23 +34546,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L405" s="5" t="n">
-        <v>6.742</v>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N405" s="5" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="O405" s="5" t="n">
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="406">
@@ -34595,13 +34569,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Deferred income tax (recovery) expense 8</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -34632,26 +34614,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K406" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L406" s="5" t="n">
-        <v>-1.495</v>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N406" s="5" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="O406" s="5" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="407">
@@ -34660,17 +34642,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>8.       NET FINANCE COSTS</t>
+        </is>
+      </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding 21 74,982,435</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>8.       NET FINANCE COSTS total</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -34701,26 +34683,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K407" s="5" t="n">
-        <v>0.000923</v>
-      </c>
-      <c r="L407" s="5" t="n">
-        <v>0.070742</v>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N407" s="5" t="n">
+        <v>5.514</v>
+      </c>
+      <c r="O407" s="5" t="n">
+        <v>5.375</v>
       </c>
     </row>
     <row r="408">
@@ -34732,14 +34714,10 @@
       <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 12,13,14, 22</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Reorganization and other related net gains 6</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -34765,26 +34743,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J408" s="5" t="n">
-        <v>5.197</v>
-      </c>
-      <c r="K408" s="5" t="n">
-        <v>8.82</v>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M408" s="5" t="n">
+        <v>-0.468</v>
+      </c>
+      <c r="N408" s="5" t="n">
+        <v>-1.327</v>
       </c>
       <c r="O408" t="inlineStr">
         <is>
@@ -34801,12 +34779,12 @@
       <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Net finance costs 6</t>
+          <t>Depreciation and amortization 12,13,14</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>InterestExpenseNonOperating</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -34834,26 +34812,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J409" s="5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K409" s="5" t="n">
-        <v>2.17</v>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M409" s="5" t="n">
+        <v>10.837</v>
+      </c>
+      <c r="N409" s="5" t="n">
+        <v>7.381</v>
       </c>
       <c r="O409" t="inlineStr">
         <is>
@@ -34870,12 +34848,12 @@
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) 7</t>
+          <t>Operating income (loss)</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -34903,26 +34881,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J410" s="5" t="n">
-        <v>-0.804</v>
-      </c>
-      <c r="K410" s="5" t="n">
-        <v>0.5</v>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M410" s="5" t="n">
+        <v>-10.856</v>
+      </c>
+      <c r="N410" s="5" t="n">
+        <v>2.081</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
@@ -34939,12 +34917,12 @@
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Net loss, being comprehensive loss for the period $</t>
+          <t>Net finance costs 7</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseNonOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -34972,26 +34950,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J411" s="5" t="n">
-        <v>-5.341</v>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>-31.792</v>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.17</v>
+      </c>
+      <c r="L411" s="5" t="n">
+        <v>5.233</v>
+      </c>
+      <c r="M411" s="5" t="n">
+        <v>5.668</v>
+      </c>
+      <c r="N411" s="5" t="n">
+        <v>5.514</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
@@ -35008,12 +34982,12 @@
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding 20 70,742,</t>
+          <t>Deferred income tax recovery 8</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -35041,21 +35015,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J412" s="5" t="n">
-        <v>58.919209</v>
-      </c>
-      <c r="K412" s="5" t="n">
-        <v>0.000923</v>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L412" s="5" t="n">
+        <v>-1.495</v>
+      </c>
+      <c r="M412" s="5" t="n">
+        <v>-0.061</v>
       </c>
       <c r="N412" t="inlineStr">
         <is>
@@ -35076,15 +35050,19 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>6.       NET FINANCE COSTS</t>
+          <t>Basic and diluted weighted average number of common</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Interest expense on debt $</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>Basic and diluted weighted average number of common shares outstanding 18</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -35110,26 +35088,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J413" s="5" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="K413" s="5" t="n">
-        <v>0.986</v>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M413" s="5" t="n">
+        <v>76.103206</v>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>76.928635</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
@@ -35143,14 +35121,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>6.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B414" t="inlineStr"/>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Interest expense on lease obligations</t>
+          <t>Impairment of non-financial assets 6,12,13,14</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -35179,16 +35153,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J414" s="5" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="K414" s="5" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L414" s="5" t="n">
+        <v>46.085</v>
       </c>
       <c r="M414" t="inlineStr">
         <is>
@@ -35212,14 +35188,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>6.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Interest expense on the Debentures, including accretion interest</t>
+          <t>Reorganization and other related (gains) costs 6</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -35248,21 +35220,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J415" s="5" t="n">
-        <v>1.309</v>
-      </c>
-      <c r="K415" s="5" t="n">
-        <v>1.092</v>
-      </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L415" s="5" t="n">
+        <v>6.742</v>
+      </c>
+      <c r="M415" s="5" t="n">
+        <v>-0.468</v>
       </c>
       <c r="N415" t="inlineStr">
         <is>
@@ -35281,19 +35253,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>6.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Depreciation and amortization 12,13,14,20</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -35321,21 +35289,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J416" s="5" t="n">
-        <v>-0.772</v>
-      </c>
-      <c r="K416" s="5" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>17.295</v>
+      </c>
+      <c r="M416" s="5" t="n">
+        <v>10.837</v>
       </c>
       <c r="N416" t="inlineStr">
         <is>
@@ -35354,19 +35322,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>6.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -35395,20 +35359,16 @@
         </is>
       </c>
       <c r="J417" s="5" t="n">
-        <v>0.083</v>
+        <v>-3.765</v>
       </c>
       <c r="K417" s="5" t="n">
-        <v>-0.126</v>
-      </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-29.122</v>
+      </c>
+      <c r="L417" s="5" t="n">
+        <v>-118.023</v>
+      </c>
+      <c r="M417" s="5" t="n">
+        <v>-10.856</v>
       </c>
       <c r="N417" t="inlineStr">
         <is>
@@ -35427,17 +35387,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>6.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Fair value (gain) loss on interest rate swaps</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr"/>
+          <t>Basic and diluted weighted average number of common shares outstanding 18</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -35463,21 +35423,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J418" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K418" s="5" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L418" s="5" t="n">
+        <v>74.982435</v>
+      </c>
+      <c r="M418" s="5" t="n">
+        <v>76.103206</v>
       </c>
       <c r="N418" t="inlineStr">
         <is>
@@ -35496,17 +35456,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>6.       NET FINANCE COSTS</t>
-        </is>
-      </c>
+      <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr">
         <is>
-          <t>6.       NET FINANCE COSTS total</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr"/>
+          <t>Depreciation and amortization 13,14,15, 23</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -35532,16 +35492,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J419" s="5" t="n">
-        <v>2.38</v>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K419" s="5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.82</v>
+      </c>
+      <c r="L419" s="5" t="n">
+        <v>17.295</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -35568,14 +35528,10 @@
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Revenue $</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Impairment of non-financial assets 6, 13,14,15</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -35586,14 +35542,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G420" s="5" t="n">
-        <v>19.79624</v>
-      </c>
-      <c r="H420" s="5" t="n">
-        <v>70.502</v>
-      </c>
-      <c r="I420" s="5" t="n">
-        <v>161.333</v>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -35605,10 +35567,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L420" s="5" t="n">
+        <v>46.085</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -35632,21 +35592,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Selling, general and administrative</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Reorganization and other related costs 6</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -35657,14 +35609,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G421" s="5" t="n">
-        <v>7.360829</v>
-      </c>
-      <c r="H421" s="5" t="n">
-        <v>23.618</v>
-      </c>
-      <c r="I421" s="5" t="n">
-        <v>58.284</v>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -35676,10 +35634,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L421" s="5" t="n">
+        <v>6.742</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -35703,19 +35659,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
+          <t>Deferred income tax (recovery) expense 8</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -35728,29 +35680,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G422" s="5" t="n">
-        <v>0.054032</v>
-      </c>
-      <c r="H422" s="5" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="I422" s="5" t="n">
-        <v>2.617</v>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K422" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L422" s="5" t="n">
+        <v>-1.495</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -35774,17 +35728,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Loss on disposal of fixed assets</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>Basic and diluted weighted average number of common shares outstanding 21 74,982,435</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -35800,8 +35754,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H423" s="5" t="n">
-        <v>0.113</v>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -35813,15 +35769,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K423" s="5" t="n">
+        <v>0.000923</v>
+      </c>
+      <c r="L423" s="5" t="n">
+        <v>0.070742</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -35845,47 +35797,47 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Depreciation and amortization 12,13,14, 22</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E424" s="5" t="n">
-        <v>0.452061</v>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G424" s="5" t="n">
-        <v>9.220271</v>
-      </c>
-      <c r="H424" s="5" t="n">
-        <v>24.192</v>
-      </c>
-      <c r="I424" s="5" t="n">
-        <v>60.901</v>
-      </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J424" s="5" t="n">
+        <v>5.197</v>
+      </c>
+      <c r="K424" s="5" t="n">
+        <v>8.82</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -35914,17 +35866,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Net finance expenses (income) 16</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>Net finance costs 6</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -35940,21 +35892,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H425" s="5" t="n">
-        <v>-0.098</v>
-      </c>
-      <c r="I425" s="5" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="J425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J425" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K425" s="5" t="n">
+        <v>2.17</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -35983,19 +35935,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B426" t="inlineStr"/>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Net loss, being comprehensive loss for the period $</t>
+          <t>Deferred income tax expense (recovery) 7</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -36013,21 +35961,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H426" s="5" t="n">
-        <v>-9.433999999999999</v>
-      </c>
-      <c r="I426" s="5" t="n">
-        <v>-20.937</v>
-      </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J426" s="5" t="n">
+        <v>-0.804</v>
+      </c>
+      <c r="K426" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -36056,19 +36004,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 17 $</t>
+          <t>Net loss, being comprehensive loss for the period $</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -36086,21 +36030,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H427" s="5" t="n">
-        <v>-1.9e-07</v>
-      </c>
-      <c r="I427" s="5" t="n">
-        <v>-3.8e-07</v>
-      </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J427" s="5" t="n">
+        <v>-5.341</v>
+      </c>
+      <c r="K427" s="5" t="n">
+        <v>-31.792</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -36129,17 +36073,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Reverse acquisition of Mira VII 5</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Basic and diluted weighted average number of common shares outstanding 20 70,742,</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -36150,8 +36094,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G428" s="5" t="n">
-        <v>1.80541</v>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
@@ -36163,15 +36109,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J428" s="5" t="n">
+        <v>58.919209</v>
+      </c>
+      <c r="K428" s="5" t="n">
+        <v>0.000923</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -36202,12 +36144,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible notes 16</t>
+          <t>Interest expense on debt $</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -36221,8 +36163,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G429" s="5" t="n">
-        <v>4.257944</v>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
@@ -36234,15 +36178,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J429" s="5" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K429" s="5" t="n">
+        <v>0.986</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -36273,19 +36213,15 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Other net finance income 15</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Interest expense on lease obligations</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -36296,26 +36232,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G430" s="5" t="n">
-        <v>-0.022431</v>
-      </c>
-      <c r="H430" s="5" t="n">
-        <v>-0.098065</v>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J430" s="5" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="K430" s="5" t="n">
+        <v>1.208</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -36346,12 +36282,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible total</t>
+          <t>Interest expense on the Debentures, including accretion interest</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -36365,26 +36301,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G431" s="5" t="n">
-        <v>4.235513</v>
-      </c>
-      <c r="H431" s="5" t="n">
-        <v>-0.098065</v>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J431" s="5" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="K431" s="5" t="n">
+        <v>1.092</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -36415,17 +36351,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Net loss, being comprehensive loss for the year $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -36438,26 +36374,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G432" s="5" t="n">
-        <v>-9.866047</v>
-      </c>
-      <c r="H432" s="5" t="n">
-        <v>-9.434588</v>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J432" s="5" t="n">
+        <v>-0.772</v>
+      </c>
+      <c r="K432" s="5" t="n">
+        <v>-0.87</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -36488,17 +36424,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Loss on remeasurement to fair value of convertible</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 17 $</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -36511,26 +36447,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G433" s="5" t="n">
-        <v>-3.2e-07</v>
-      </c>
-      <c r="H433" s="5" t="n">
-        <v>-1.9e-07</v>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J433" s="5" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="K433" s="5" t="n">
+        <v>-0.126</v>
       </c>
       <c r="L433" t="inlineStr">
         <is>
@@ -36561,17 +36497,19 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Expenses relating to identification of qualifying transaction $</t>
+          <t>Fair value (gain) loss on interest rate swaps</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
-      <c r="E434" s="5" t="n">
-        <v>0.226169</v>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36593,15 +36531,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J434" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K434" s="5" t="n">
+        <v>-0.12</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
@@ -36632,17 +36566,19 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>6.       NET FINANCE COSTS</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Stock based compensation (Note 9 (b))</t>
+          <t>6.       NET FINANCE COSTS total</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
-      <c r="E435" s="5" t="n">
-        <v>0.1125</v>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36664,15 +36600,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J435" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K435" s="5" t="n">
+        <v>2.17</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
@@ -36701,43 +36633,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Revenue $</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E436" s="5" t="n">
-        <v>0.044921</v>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F436" s="5" t="n">
+        <v>2.80166</v>
+      </c>
+      <c r="G436" s="5" t="n">
+        <v>19.79624</v>
+      </c>
+      <c r="H436" s="5" t="n">
+        <v>70.502</v>
+      </c>
+      <c r="I436" s="5" t="n">
+        <v>161.333</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -36783,36 +36705,30 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Selling, general and administrative</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E437" s="5" t="n">
-        <v>-0.000311</v>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F437" s="5" t="n">
+        <v>1.132721</v>
+      </c>
+      <c r="G437" s="5" t="n">
+        <v>7.360829</v>
+      </c>
+      <c r="H437" s="5" t="n">
+        <v>23.618</v>
+      </c>
+      <c r="I437" s="5" t="n">
+        <v>58.284</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
@@ -36858,36 +36774,30 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E438" s="5" t="n">
-        <v>0.068782</v>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F438" s="5" t="n">
+        <v>0.009741</v>
+      </c>
+      <c r="G438" s="5" t="n">
+        <v>0.054032</v>
+      </c>
+      <c r="H438" s="5" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="I438" s="5" t="n">
+        <v>2.617</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -36933,31 +36843,25 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E439" s="5" t="n">
-        <v>-0.452061</v>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss on disposal of fixed assets</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F439" s="5" t="n">
+        <v>0.008466</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H439" s="5" t="n">
+        <v>0.113</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -37003,37 +36907,33 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Net loss per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Basic and fully diluted (Note 10) $</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E440" s="5" t="n">
-        <v>2e-07</v>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.452061</v>
+      </c>
+      <c r="F440" s="5" t="n">
+        <v>1.150928</v>
+      </c>
+      <c r="G440" s="5" t="n">
+        <v>9.220271</v>
+      </c>
+      <c r="H440" s="5" t="n">
+        <v>24.192</v>
+      </c>
+      <c r="I440" s="5" t="n">
+        <v>60.901</v>
       </c>
       <c r="J440" t="inlineStr">
         <is>
@@ -37074,64 +36974,1500 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Net finance expenses (income) 16</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H441" s="5" t="n">
+        <v>-0.098</v>
+      </c>
+      <c r="I441" s="5" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Net loss, being comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H442" s="5" t="n">
+        <v>-9.433999999999999</v>
+      </c>
+      <c r="I442" s="5" t="n">
+        <v>-20.937</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 17 $</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H443" s="5" t="n">
+        <v>-1.9e-07</v>
+      </c>
+      <c r="I443" s="5" t="n">
+        <v>-3.8e-07</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Reverse acquisition of Mira VII 5</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G444" s="5" t="n">
+        <v>1.80541</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible notes 16</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G445" s="5" t="n">
+        <v>4.257944</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Other net finance income 15</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G446" s="5" t="n">
+        <v>-0.022431</v>
+      </c>
+      <c r="H446" s="5" t="n">
+        <v>-0.098065</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible total</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F447" s="5" t="n">
+        <v>0.355483</v>
+      </c>
+      <c r="G447" s="5" t="n">
+        <v>4.235513</v>
+      </c>
+      <c r="H447" s="5" t="n">
+        <v>-0.098065</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Net loss, being comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F448" s="5" t="n">
+        <v>-1.239171</v>
+      </c>
+      <c r="G448" s="5" t="n">
+        <v>-9.866047</v>
+      </c>
+      <c r="H448" s="5" t="n">
+        <v>-9.434588</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share 17 $</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G449" s="5" t="n">
+        <v>-3.2e-07</v>
+      </c>
+      <c r="H449" s="5" t="n">
+        <v>-1.9e-07</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Reverse acquisition of Mira VII (note 5)</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G450" s="5" t="n">
+        <v>1.80541</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible notes (note 21)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F451" s="5" t="n">
+        <v>0.345194</v>
+      </c>
+      <c r="G451" s="5" t="n">
+        <v>4.257944</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Other net finance (income) expenses (note 15)</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F452" s="5" t="n">
+        <v>0.010289</v>
+      </c>
+      <c r="G452" s="5" t="n">
+        <v>-0.022431</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Loss on remeasurement to fair value of convertible</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 16) $</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F453" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="G453" s="5" t="n">
+        <v>-3.2e-07</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying transaction $</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" s="5" t="n">
+        <v>0.226169</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Stock based compensation (Note 9 (b))</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" s="5" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E456" s="5" t="n">
+        <v>0.044921</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E457" s="5" t="n">
+        <v>-0.000311</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E458" s="5" t="n">
+        <v>0.068782</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E459" s="5" t="n">
+        <v>-0.452061</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Net loss per common share</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" s="5" t="n">
+        <v>2e-07</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="C461" t="inlineStr">
         <is>
           <t>Basic and fully diluted (Note 10)</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
-      <c r="E441" s="5" t="n">
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" s="5" t="n">
         <v>2.226148</v>
       </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O441" t="inlineStr">
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
         <is>
           <t>-</t>
         </is>
